--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 18/06/2026, 11:47</x:t>
+    <x:t>Conta: 4163084 | 23/06/2026, 13:56</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.758,25</x:t>
+    <x:t>R$ 2.736,63</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
@@ -70,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>5758,25</x:t>
+    <x:t>2736,63</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -674,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5758.25</x:v>
+        <x:v>2736.63</x:v>
       </x:c>
       <x:c r="B4" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>5758.25</x:v>
+        <x:v>2736.63</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 23/06/2026, 13:56</x:t>
+    <x:t>Conta: 4163084 | 24/06/2026, 16:29</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 24/06/2026, 16:29</x:t>
+    <x:t>Conta: 4163084 | 26/06/2026, 17:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 26/06/2026, 17:04</x:t>
+    <x:t>Conta: 4163084 | 29/06/2026, 11:43</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 29/06/2026, 11:43</x:t>
+    <x:t>Conta: 4163084 | 30/06/2026, 20:07</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 30/06/2026, 20:07</x:t>
+    <x:t>Conta: 4163084 | 01/07/2026, 18:17</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 01/07/2026, 18:17</x:t>
+    <x:t>Conta: 4163084 | 03/07/2026, 15:18</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 03/07/2026, 15:18</x:t>
+    <x:t>Conta: 4163084 | 06/07/2026, 17:14</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,15 +34,72 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.736,63</x:t>
+    <x:t>99,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.203.635,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,90%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.171.532,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.201.313,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.203.113,20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,05%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.737,83</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -70,7 +127,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>2736,63</x:t>
+    <x:t>2737,83</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -614,7 +671,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -674,13 +731,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2736.63</x:v>
+        <x:v>5206373.58405128</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>0</x:v>
+        <x:v>5203635.75405128</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>2736.63</x:v>
+        <x:v>2737.83</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -728,13 +785,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="9"/>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="G7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -744,45 +801,43 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
       <x:c r="A10" s="12" t="s">
@@ -792,38 +847,150 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="9"/>
+      <x:c r="H12" s="9"/>
+      <x:c r="I12" s="9"/>
+      <x:c r="J12" s="9"/>
+      <x:c r="K12" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="3">
+  <x:mergeCells count="4">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A12:J12"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 06/07/2026, 17:14</x:t>
+    <x:t>Conta: 4163084 | 07/07/2026, 15:56</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>99,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.203.635,75</x:t>
+    <x:t>R$ 5.205.959,25</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -70,9 +70,6 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>DEB</x:t>
-  </x:si>
-  <x:si>
     <x:t>03/07/2026</x:t>
   </x:si>
   <x:si>
@@ -91,7 +88,7 @@
     <x:t>R$ 5.201.313,30</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.203.113,20</x:t>
+    <x:t>R$ 5.204.913,91</x:t>
   </x:si>
   <x:si>
     <x:t>0,05%|Saldo projetado</x:t>
@@ -731,10 +728,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5206373.58405128</x:v>
+        <x:v>5208697.0801098</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5203635.75405128</x:v>
+        <x:v>5205959.2501098</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2737.83</x:v>
@@ -840,35 +837,31 @@
       <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12" t="s">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="s">
+      <x:c r="C10" s="12"/>
+      <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="s">
+      <x:c r="E10" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E10" s="12" t="s">
+      <x:c r="F10" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="s">
+      <x:c r="G10" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="s">
+      <x:c r="H10" s="12" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
@@ -887,7 +880,7 @@
     </x:row>
     <x:row r="12" spans="1:11" ht="45" customHeight="1">
       <x:c r="A12" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="9"/>
       <x:c r="C12" s="9"/>
@@ -899,7 +892,7 @@
       <x:c r="I12" s="9"/>
       <x:c r="J12" s="9"/>
       <x:c r="K12" s="10" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -923,66 +916,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="s">
+      <x:c r="E14" s="11" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="F14" s="11" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="G14" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="H14" s="11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="s">
+      <x:c r="I14" s="11" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="s">
+      <x:c r="J14" s="11" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="J14" s="11" t="s">
+      <x:c r="K14" s="11" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
       <x:c r="A15" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B15" s="12" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="C15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K15" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 07/07/2026, 15:56</x:t>
+    <x:t>Conta: 4163084 | 09/07/2026, 18:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>99,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.205.959,25</x:t>
+    <x:t>R$ 5.210.609,35</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -88,7 +88,7 @@
     <x:t>R$ 5.201.313,30</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.204.913,91</x:t>
+    <x:t>R$ 5.208.517,74</x:t>
   </x:si>
   <x:si>
     <x:t>0,05%|Saldo projetado</x:t>
@@ -728,10 +728,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5208697.0801098</x:v>
+        <x:v>5213347.1803282</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5205959.2501098</x:v>
+        <x:v>5210609.3503282</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>2737.83</x:v>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 09/07/2026, 18:04</x:t>
+    <x:t>Conta: 4163084 | 14/07/2026, 09:57</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>99,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.210.609,35</x:t>
+    <x:t>R$ 3.215.146,15</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -79,22 +79,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>3.171.532,00</x:t>
+    <x:t>1.954.338,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 5.201.313,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.208.517,74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,05%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.737,83</x:t>
+    <x:t>R$ 3.205.114,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.212.889,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,08%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.723,35</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -124,7 +124,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>2737,83</x:t>
+    <x:t>2723,35</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -728,13 +728,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>5213347.1803282</x:v>
+        <x:v>3217869.50193118</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>5210609.3503282</x:v>
+        <x:v>3215146.15193118</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>2737.83</x:v>
+        <x:v>2723.35</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 14/07/2026, 09:57</x:t>
+    <x:t>Conta: 4163084 | 15/07/2026, 19:01</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,69 +34,15 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>99,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.215.146,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,90%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
+    <x:t>100%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000,00</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.954.338,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.205.114,83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.212.889,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,08%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.723,35</x:t>
-  </x:si>
-  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -124,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>2723,35</x:t>
+    <x:t>1000</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -668,7 +614,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K15"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -728,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3217869.50193118</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3215146.15193118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>2723.35</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -782,13 +728,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="9"/>
+      <x:c r="J7" s="9"/>
+      <x:c r="K7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -798,192 +744,86 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="s">
+      <x:c r="C9" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="D9" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="E9" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="F9" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="G9" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="H9" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="s">
+      <x:c r="I9" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="s">
+      <x:c r="J9" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="s">
+      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="4"/>
-      <x:c r="B11" s="4"/>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9"/>
-      <x:c r="I12" s="9"/>
-      <x:c r="J12" s="9"/>
-      <x:c r="K12" s="10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A14" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="3">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:J12"/>
+    <x:mergeCell ref="A7:J7"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 15/07/2026, 19:01</x:t>
+    <x:t>Conta: 4163084 | 21/07/2026, 09:17</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 21/07/2026, 09:17</x:t>
+    <x:t>Conta: 4163084 | 27/07/2026, 15:22</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 27/07/2026, 15:22</x:t>
+    <x:t>Conta: 4163084 | 29/07/2026, 18:28</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 29/07/2026, 18:28</x:t>
+    <x:t>Conta: 4163084 | 30/07/2026, 16:38</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 30/07/2026, 16:38</x:t>
+    <x:t>Conta: 4163084 | 04/08/2026, 17:39</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 04/08/2026, 17:39</x:t>
+    <x:t>Conta: 4163084 | 11/08/2026, 16:37</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,15 +34,84 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.000,00</x:t>
+    <x:t>99,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.520,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,90%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>737,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.002.540,45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.003.861,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.003.564,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>751,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 997.343,96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 998.658,37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 998.362,63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,06%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.276,39</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -70,7 +139,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>1000</x:t>
+    <x:t>1276,39</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -266,7 +335,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -312,6 +381,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -614,7 +687,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -674,13 +747,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1000</x:v>
+        <x:v>2003796.46089022</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>0</x:v>
+        <x:v>2002520.07089022</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>1000</x:v>
+        <x:v>1276.39</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -728,13 +801,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="9"/>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="G7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -744,86 +817,221 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12" t="s">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
+      <x:c r="C10" s="12"/>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A11" s="13"/>
+      <x:c r="B11" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="13"/>
+      <x:c r="D11" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="E11" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H11" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K11" s="3"/>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A13" s="8" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="G13" s="9"/>
+      <x:c r="H13" s="9"/>
+      <x:c r="I13" s="9"/>
+      <x:c r="J13" s="9"/>
+      <x:c r="K13" s="10" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A15" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K15" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K16" s="13" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="3">
+  <x:mergeCells count="4">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A13:J13"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 11/08/2026, 16:37</x:t>
+    <x:t>Conta: 4163084 | 17/08/2026, 14:25</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,84 +34,15 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>99,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.002.520,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,90%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
+    <x:t>100%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.409,31</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>737,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.002.540,45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.003.861,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.003.564,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>751,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 997.343,96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 998.658,37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 998.362,63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,06%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.276,39</x:t>
-  </x:si>
-  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -139,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>1276,39</x:t>
+    <x:t>1409,31</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -335,7 +266,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -381,10 +312,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -687,7 +614,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K16"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -747,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>2003796.46089022</x:v>
+        <x:v>1409.31</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>2002520.07089022</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>1276.39</x:v>
+        <x:v>1409.31</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -801,13 +728,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="9"/>
+      <x:c r="J7" s="9"/>
+      <x:c r="K7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -817,221 +744,86 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="s">
+      <x:c r="C9" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="D9" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="E9" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="F9" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="G9" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="H9" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="s">
+      <x:c r="I9" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="s">
+      <x:c r="J9" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="s">
+      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="13"/>
-      <x:c r="B11" s="13" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="13"/>
-      <x:c r="D11" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E11" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G11" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H11" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I11" s="13" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="J11" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K11" s="3"/>
-    </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A13" s="8" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B13" s="9"/>
-      <x:c r="C13" s="9"/>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9"/>
-      <x:c r="I13" s="9"/>
-      <x:c r="J13" s="9"/>
-      <x:c r="K13" s="10" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A15" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J15" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K15" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K16" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="3">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A13:J13"/>
+    <x:mergeCell ref="A7:J7"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 17/08/2026, 14:25</x:t>
+    <x:t>Conta: 4163084 | 18/08/2026, 09:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.409,31</x:t>
+    <x:t>R$ 28.001.409,31</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
@@ -70,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>1409,31</x:t>
+    <x:t>28001409,31</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -674,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1409.31</x:v>
+        <x:v>28001409.31</x:v>
       </x:c>
       <x:c r="B4" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>1409.31</x:v>
+        <x:v>28001409.31</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 18/08/2026, 09:40</x:t>
+    <x:t>Conta: 4163084 | 18/08/2026, 10:45</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,15 +34,135 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 28.001.409,31</x:t>
+    <x:t>17,8%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.997.129,46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,80%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LCA BNDES - JUN/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/06/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/06/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83,50% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>432,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53,6%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 15.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qtd. cotas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Em cotização</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 271,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.363,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.000.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 141,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.175,54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,6%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.004.279,86</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -70,7 +190,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>28001409,31</x:t>
+    <x:t>8004279,86</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -266,7 +386,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -316,6 +436,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -614,10 +738,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -674,13 +798,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>28001409.31</x:v>
+        <x:v>28001409.3176</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>0</x:v>
+        <x:v>19997129.4576</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>28001409.31</x:v>
+        <x:v>8004279.86</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -728,13 +852,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="9"/>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="G7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -744,45 +868,43 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
       <x:c r="A10" s="12" t="s">
@@ -792,38 +914,410 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H12" s="3"/>
+      <x:c r="I12" s="3"/>
+      <x:c r="J12" s="3"/>
+      <x:c r="K12" s="3"/>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="3"/>
+      <x:c r="I13" s="3"/>
+      <x:c r="J13" s="3"/>
+      <x:c r="K13" s="3"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="3"/>
+      <x:c r="I14" s="3"/>
+      <x:c r="J14" s="3"/>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s">
+      <x:c r="C15" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H15" s="3"/>
+      <x:c r="I15" s="3"/>
+      <x:c r="J15" s="3"/>
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E10" s="12" t="s">
+      <x:c r="C16" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="3"/>
+      <x:c r="J16" s="3"/>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="s">
+      <x:c r="C17" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="3"/>
+      <x:c r="J17" s="3"/>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A18" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="s">
+      <x:c r="C18" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A19" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H10" s="12" t="s">
+      <x:c r="C19" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H19" s="3"/>
+      <x:c r="I19" s="3"/>
+      <x:c r="J19" s="3"/>
+      <x:c r="K19" s="3"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A20" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="I10" s="12" t="s">
+      <x:c r="C20" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H20" s="3"/>
+      <x:c r="I20" s="3"/>
+      <x:c r="J20" s="3"/>
+      <x:c r="K20" s="3"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="C21" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H21" s="3"/>
+      <x:c r="I21" s="3"/>
+      <x:c r="J21" s="3"/>
+      <x:c r="K21" s="3"/>
+    </x:row>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A23" s="8" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B23" s="9"/>
+      <x:c r="C23" s="9"/>
+      <x:c r="D23" s="9"/>
+      <x:c r="E23" s="9"/>
+      <x:c r="F23" s="9"/>
+      <x:c r="G23" s="9"/>
+      <x:c r="H23" s="9"/>
+      <x:c r="I23" s="9"/>
+      <x:c r="J23" s="9"/>
+      <x:c r="K23" s="10" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:11">
+      <x:c r="A24" s="4"/>
+      <x:c r="B24" s="4"/>
+      <x:c r="C24" s="4"/>
+      <x:c r="D24" s="4"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A25" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J25" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K25" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J26" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K26" s="12" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="3">
+  <x:mergeCells count="5">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A12:F12"/>
+    <x:mergeCell ref="A23:J23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 18/08/2026, 10:45</x:t>
+    <x:t>Conta: 4163084 | 18/08/2026, 13:31</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -139,13 +139,31 @@
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 1,92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.080.503,91</x:t>
+  </x:si>
+  <x:si>
     <x:t>R$ 4.000.000,00</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 1.437,40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.391,40</x:t>
+  </x:si>
+  <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.362.148,59</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
@@ -1098,19 +1116,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D18" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E18" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="F18" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G18" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
@@ -1119,25 +1137,25 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="30" customHeight="1">
       <x:c r="A19" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D19" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E19" s="13" t="s">
+      <x:c r="F19" s="13" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F19" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="G19" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1146,25 +1164,25 @@
     </x:row>
     <x:row r="20" spans="1:11" ht="30" customHeight="1">
       <x:c r="A20" s="13" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D20" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E20" s="13" t="s">
+      <x:c r="F20" s="13" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F20" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="G20" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1173,16 +1191,16 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
         <x:v>35</x:v>
@@ -1213,7 +1231,7 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="45" customHeight="1">
       <x:c r="A23" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B23" s="9"/>
       <x:c r="C23" s="9"/>
@@ -1225,7 +1243,7 @@
       <x:c r="I23" s="9"/>
       <x:c r="J23" s="9"/>
       <x:c r="K23" s="10" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1249,66 +1267,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="11" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D25" s="11" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E25" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F25" s="11" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G25" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H25" s="11" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I25" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J25" s="11" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K25" s="11" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K26" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 18/08/2026, 13:31</x:t>
+    <x:t>Conta: 4163084 | 18/08/2026, 14:34</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -91,6 +91,24 @@
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
+    <x:t>28,6%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.003.999,97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,50%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.680.701,00</x:t>
+  </x:si>
+  <x:si>
     <x:t>53,6%|Fundos de Investimento</x:t>
   </x:si>
   <x:si>
@@ -175,10 +193,7 @@
     <x:t>14.175,54</x:t>
   </x:si>
   <x:si>
-    <x:t>28,6%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.004.279,86</x:t>
+    <x:t>R$ 279,89</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -208,7 +223,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>8004279,86</x:t>
+    <x:t>279,89</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -756,7 +771,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K26"/>
+  <x:dimension ref="A1:K31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -816,13 +831,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>28001409.3176</x:v>
+        <x:v>28001409.3213893</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>19997129.4576</x:v>
+        <x:v>28001129.4313893</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>8004279.86</x:v>
+        <x:v>279.89</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1005,157 +1020,127 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="12" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="E15" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="s">
+      <x:c r="F15" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="G15" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="4"/>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A17" s="8" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="13" t="s">
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="9"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B15" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D15" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E15" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F15" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H15" s="3"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
-      <x:c r="K15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B16" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H16" s="3"/>
-      <x:c r="I16" s="3"/>
-      <x:c r="J16" s="3"/>
-      <x:c r="K16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A17" s="13" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B17" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C17" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D17" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F17" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
       <x:c r="J17" s="3"/>
       <x:c r="K17" s="3"/>
     </x:row>
-    <x:row r="18" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A18" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B18" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C18" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D18" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E18" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F18" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G18" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A19" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B19" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C19" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D19" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E19" s="13" t="s">
+    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A19" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F19" s="13" t="s">
+      <x:c r="D19" s="11" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G19" s="13" t="s">
-        <x:v>36</x:v>
+      <x:c r="E19" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
@@ -1164,25 +1149,25 @@
     </x:row>
     <x:row r="20" spans="1:11" ht="30" customHeight="1">
       <x:c r="A20" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D20" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E20" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G20" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1190,152 +1175,288 @@
       <x:c r="K20" s="3"/>
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B21" s="12" t="s">
+      <x:c r="A21" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C21" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E21" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F21" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="s">
-        <x:v>36</x:v>
+      <x:c r="C21" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
       <x:c r="J21" s="3"/>
       <x:c r="K21" s="3"/>
     </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="A22" s="4"/>
-      <x:c r="B22" s="4"/>
-      <x:c r="C22" s="4"/>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A23" s="8" t="s">
+    <x:row r="22" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A22" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H22" s="3"/>
+      <x:c r="I22" s="3"/>
+      <x:c r="J22" s="3"/>
+      <x:c r="K22" s="3"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A23" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G23" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H23" s="3"/>
+      <x:c r="I23" s="3"/>
+      <x:c r="J23" s="3"/>
+      <x:c r="K23" s="3"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A24" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G24" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H24" s="3"/>
+      <x:c r="I24" s="3"/>
+      <x:c r="J24" s="3"/>
+      <x:c r="K24" s="3"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A25" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
-      <x:c r="D23" s="9"/>
-      <x:c r="E23" s="9"/>
-      <x:c r="F23" s="9"/>
-      <x:c r="G23" s="9"/>
-      <x:c r="H23" s="9"/>
-      <x:c r="I23" s="9"/>
-      <x:c r="J23" s="9"/>
-      <x:c r="K23" s="10" t="s">
+      <x:c r="B25" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="s">
         <x:v>54</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="A24" s="4"/>
-      <x:c r="B24" s="4"/>
-      <x:c r="C24" s="4"/>
-      <x:c r="D24" s="4"/>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A25" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B25" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C25" s="11" t="s">
+      <x:c r="D25" s="13" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D25" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I25" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J25" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K25" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
+      <x:c r="E25" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G25" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H25" s="3"/>
+      <x:c r="I25" s="3"/>
+      <x:c r="J25" s="3"/>
+      <x:c r="K25" s="3"/>
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="12" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E26" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G26" s="12" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H26" s="3"/>
+      <x:c r="I26" s="3"/>
+      <x:c r="J26" s="3"/>
+      <x:c r="K26" s="3"/>
+    </x:row>
+    <x:row r="27" spans="1:11">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="4"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="4"/>
+      <x:c r="J27" s="4"/>
+      <x:c r="K27" s="4"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A28" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
+      <x:c r="D28" s="9"/>
+      <x:c r="E28" s="9"/>
+      <x:c r="F28" s="9"/>
+      <x:c r="G28" s="9"/>
+      <x:c r="H28" s="9"/>
+      <x:c r="I28" s="9"/>
+      <x:c r="J28" s="9"/>
+      <x:c r="K28" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:11">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="4"/>
+      <x:c r="G29" s="4"/>
+      <x:c r="H29" s="4"/>
+      <x:c r="I29" s="4"/>
+      <x:c r="J29" s="4"/>
+      <x:c r="K29" s="4"/>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A30" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B26" s="12" t="s">
+      <x:c r="H30" s="11" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="I26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="J26" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K26" s="12" t="s">
-        <x:v>65</x:v>
+      <x:c r="I30" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K30" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A31" s="12" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J31" s="12" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K31" s="12" t="s">
+        <x:v>70</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="5">
+  <x:mergeCells count="6">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A23:J23"/>
+    <x:mergeCell ref="A17:F17"/>
+    <x:mergeCell ref="A28:J28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 18/08/2026, 14:34</x:t>
+    <x:t>Conta: 4163084 | 18/08/2026, 18:42</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 18/08/2026, 18:42</x:t>
+    <x:t>Conta: 4163084 | 20/08/2026, 09:48</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,70 +34,73 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>17,8%|Renda Fixa</x:t>
+    <x:t>18,5%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.001.441,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,50%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Garantia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LCA BNDES - JUN/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/06/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/06/2028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83,50% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>432,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 4.997.129,46</x:t>
   </x:si>
   <x:si>
-    <x:t>17,80%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Garantia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LCA BNDES - JUN/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27/06/2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/06/2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83,50% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>432,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28,6%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 8.003.999,97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28,50%|Pós-Fixada</x:t>
+    <x:t>25,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 7.010.491,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>21/09/2026</x:t>
@@ -106,16 +109,22 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>4.680.701,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53,6%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 15.000.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>4.096.104,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 7.004.338,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 7.009.107,30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,5%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 15.006.235,91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -133,7 +142,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 271,60</x:t>
+    <x:t>19/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 271,75</x:t>
   </x:si>
   <x:si>
     <x:t>7.363,69</x:t>
@@ -142,18 +154,33 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.000.000,00</x:t>
+    <x:t>R$ 2.001.067,49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.033,10</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 44,73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33.531,12</x:t>
+  </x:si>
+  <x:si>
     <x:t>R$ 1.500.000,00</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 1,98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>757.260,27</x:t>
+  </x:si>
+  <x:si>
     <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
   </x:si>
   <x:si>
@@ -163,18 +190,27 @@
     <x:t>2.080.503,91</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.000.000,00</x:t>
+    <x:t>R$ 4.002.088,51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.000.064,75</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.437,40</x:t>
+    <x:t>R$ 1.438,19</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 2.001.089,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.033,76</x:t>
+  </x:si>
+  <x:si>
     <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
   </x:si>
   <x:si>
@@ -184,16 +220,28 @@
     <x:t>1.362.148,59</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 2.001.041,36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.032,28</x:t>
+  </x:si>
+  <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,09</x:t>
+    <x:t>R$ 141,16</x:t>
   </x:si>
   <x:si>
     <x:t>14.175,54</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 279,89</x:t>
+    <x:t>R$ 2.000.949,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.029,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 281,11</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -223,7 +271,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>279,89</x:t>
+    <x:t>281,11</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -831,13 +879,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>28001409.3213893</x:v>
+        <x:v>27018450.2037533</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>28001129.4313893</x:v>
+        <x:v>27018169.0937533</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>279.89</x:v>
+        <x:v>281.11</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -962,7 +1010,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
         <x:v>7</x:v>
@@ -987,7 +1035,7 @@
     </x:row>
     <x:row r="12" spans="1:11" ht="45" customHeight="1">
       <x:c r="A12" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="9"/>
       <x:c r="C12" s="9"/>
@@ -995,7 +1043,7 @@
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="10" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H12" s="3"/>
       <x:c r="I12" s="3"/>
@@ -1017,7 +1065,7 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A14" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
         <x:v>9</x:v>
@@ -1055,25 +1103,25 @@
       </x:c>
       <x:c r="C15" s="12"/>
       <x:c r="D15" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G15" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H15" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K15" s="3"/>
     </x:row>
@@ -1092,7 +1140,7 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="45" customHeight="1">
       <x:c r="A17" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
@@ -1100,7 +1148,7 @@
       <x:c r="E17" s="9"/>
       <x:c r="F17" s="9"/>
       <x:c r="G17" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
@@ -1122,19 +1170,19 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A19" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B19" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="11" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D19" s="11" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E19" s="11" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F19" s="11" t="s">
         <x:v>16</x:v>
@@ -1149,25 +1197,25 @@
     </x:row>
     <x:row r="20" spans="1:11" ht="30" customHeight="1">
       <x:c r="A20" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="13" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D20" s="13" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E20" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F20" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G20" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
@@ -1176,25 +1224,25 @@
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="13" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D21" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F21" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G21" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
@@ -1203,25 +1251,25 @@
     </x:row>
     <x:row r="22" spans="1:11" ht="30" customHeight="1">
       <x:c r="A22" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F22" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G22" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H22" s="3"/>
       <x:c r="I22" s="3"/>
@@ -1230,25 +1278,25 @@
     </x:row>
     <x:row r="23" spans="1:11" ht="30" customHeight="1">
       <x:c r="A23" s="13" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C23" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D23" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E23" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F23" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G23" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H23" s="3"/>
       <x:c r="I23" s="3"/>
@@ -1257,25 +1305,25 @@
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
       <x:c r="A24" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B24" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E24" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F24" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G24" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H24" s="3"/>
       <x:c r="I24" s="3"/>
@@ -1284,25 +1332,25 @@
     </x:row>
     <x:row r="25" spans="1:11" ht="30" customHeight="1">
       <x:c r="A25" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B25" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E25" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F25" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G25" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H25" s="3"/>
       <x:c r="I25" s="3"/>
@@ -1311,25 +1359,25 @@
     </x:row>
     <x:row r="26" spans="1:11" ht="30" customHeight="1">
       <x:c r="A26" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C26" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G26" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H26" s="3"/>
       <x:c r="I26" s="3"/>
@@ -1363,7 +1411,7 @@
       <x:c r="I28" s="9"/>
       <x:c r="J28" s="9"/>
       <x:c r="K28" s="10" t="s">
-        <x:v>59</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -1387,66 +1435,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="11" t="s">
-        <x:v>60</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D30" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E30" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F30" s="11" t="s">
-        <x:v>63</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G30" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H30" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I30" s="11" t="s">
-        <x:v>66</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J30" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K30" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11" ht="30" customHeight="1">
       <x:c r="A31" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K31" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 4163084.xlsx
+++ b/data/positions/Posição Consolidada - 4163084.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 4163084 | 20/08/2026, 09:48</x:t>
+    <x:t>Conta: 4163084 | 21/08/2026, 14:50</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>18,5%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 5.001.441,52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,50%|Pós-Fixada</x:t>
+    <x:t>38,4%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 5.003.598,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,37 +94,13 @@
     <x:t>R$ 4.997.129,46</x:t>
   </x:si>
   <x:si>
-    <x:t>25,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 7.010.491,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,90%|Pós-Fixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.096.104,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 7.004.338,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 7.009.107,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,5%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 15.006.235,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>61,5%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 8.008.443,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61,50%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -142,34 +118,40 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
+    <x:t>20/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 271,88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.363,69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.002.066,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.112,10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
+  </x:si>
+  <x:si>
     <x:t>19/08/2026</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 271,75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.363,69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.067,49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.033,10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safra Vitesse Classe de Investimento RF CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 44,73</x:t>
+    <x:t>R$ 44,76</x:t>
   </x:si>
   <x:si>
     <x:t>33.531,12</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.500.000,00</x:t>
+    <x:t>R$ 1.500.783,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.024,29</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco Zupo FIF CIC RF CP LP RL</x:t>
@@ -181,67 +163,49 @@
     <x:t>757.260,27</x:t>
   </x:si>
   <x:si>
-    <x:t>XP Bancos FIRF Referenciada DI CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.080.503,91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.002.088,51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.000.064,75</x:t>
+    <x:t>R$ 1.501.549,35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.084,05</x:t>
   </x:si>
   <x:si>
     <x:t>Bradesco SKY FIC FIRF Referenciada DI RL</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.438,19</x:t>
+    <x:t>21/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.439,63</x:t>
   </x:si>
   <x:si>
     <x:t>1.391,40</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.001.089,07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.033,76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bradesco Bancos II FIF CIC RF CP RL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1,47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.362.148,59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.001.041,36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.032,28</x:t>
+    <x:t>R$ 2.003.092,53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.000.239,67</x:t>
   </x:si>
   <x:si>
     <x:t>Safra Extra Bancos Special FIC FIRF CP</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 141,16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.175,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.949,48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.000.029,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 281,11</x:t>
+    <x:t>R$ 141,23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.087,60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.952,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.000.029,01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,08%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 9.800,75</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -271,7 +235,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>281,11</x:t>
+    <x:t>9800,75</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -819,7 +783,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K31"/>
+  <x:dimension ref="A1:K24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
@@ -879,13 +843,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>27018450.2037533</x:v>
+        <x:v>13021843.2277658</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>27018169.0937533</x:v>
+        <x:v>13012042.4777658</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>281.11</x:v>
+        <x:v>9800.75</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1068,443 +1032,283 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G14" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="H14" s="3"/>
+      <x:c r="I14" s="3"/>
+      <x:c r="J14" s="3"/>
       <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
+      <x:c r="A15" s="13" t="s">
         <x:v>33</x:v>
       </x:c>
+      <x:c r="B15" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H15" s="3"/>
+      <x:c r="I15" s="3"/>
+      <x:c r="J15" s="3"/>
       <x:c r="K15" s="3"/>
     </x:row>
-    <x:row r="16" spans="1:11">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A17" s="8" t="s">
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="3"/>
+      <x:c r="J16" s="3"/>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="10" t="s">
-        <x:v>35</x:v>
+      <x:c r="C17" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="3"/>
       <x:c r="I17" s="3"/>
       <x:c r="J17" s="3"/>
       <x:c r="K17" s="3"/>
     </x:row>
-    <x:row r="18" spans="1:11">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
+    <x:row r="18" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A18" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="H18" s="3"/>
       <x:c r="I18" s="3"/>
       <x:c r="J18" s="3"/>
       <x:c r="K18" s="3"/>
     </x:row>
-    <x:row r="19" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A19" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="s">
+    <x:row r="19" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A19" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C19" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E19" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="s">
-        <x:v>17</x:v>
+      <x:c r="F19" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A20" s="13" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B20" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C20" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D20" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E20" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F20" s="13" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G20" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H20" s="3"/>
-      <x:c r="I20" s="3"/>
-      <x:c r="J20" s="3"/>
-      <x:c r="K20" s="3"/>
-    </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C21" s="13" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D21" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E21" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F21" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H21" s="3"/>
-      <x:c r="I21" s="3"/>
-      <x:c r="J21" s="3"/>
-      <x:c r="K21" s="3"/>
-    </x:row>
-    <x:row r="22" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A22" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D22" s="13" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E22" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F22" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G22" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H22" s="3"/>
-      <x:c r="I22" s="3"/>
-      <x:c r="J22" s="3"/>
-      <x:c r="K22" s="3"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A23" s="13" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B23" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H23" s="3"/>
-      <x:c r="I23" s="3"/>
-      <x:c r="J23" s="3"/>
-      <x:c r="K23" s="3"/>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
+      <x:c r="H20" s="4"/>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="4"/>
+      <x:c r="K20" s="4"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A21" s="8" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B21" s="9"/>
+      <x:c r="C21" s="9"/>
+      <x:c r="D21" s="9"/>
+      <x:c r="E21" s="9"/>
+      <x:c r="F21" s="9"/>
+      <x:c r="G21" s="9"/>
+      <x:c r="H21" s="9"/>
+      <x:c r="I21" s="9"/>
+      <x:c r="J21" s="9"/>
+      <x:c r="K21" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A23" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J23" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K23" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B24" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="13" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D24" s="13" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E24" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F24" s="13" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G24" s="13" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H24" s="3"/>
-      <x:c r="I24" s="3"/>
-      <x:c r="J24" s="3"/>
-      <x:c r="K24" s="3"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A25" s="13" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B25" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C25" s="13" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D25" s="13" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E25" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F25" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G25" s="13" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H25" s="3"/>
-      <x:c r="I25" s="3"/>
-      <x:c r="J25" s="3"/>
-      <x:c r="K25" s="3"/>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A26" s="12" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B26" s="12" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C26" s="12" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D26" s="12" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E26" s="12" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F26" s="12" t="s">
+      <x:c r="A24" s="12" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="s">
+      <x:c r="B24" s="12" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="H26" s="3"/>
-      <x:c r="I26" s="3"/>
-      <x:c r="J26" s="3"/>
-      <x:c r="K26" s="3"/>
-    </x:row>
-    <x:row r="27" spans="1:11">
-      <x:c r="A27" s="4"/>
-      <x:c r="B27" s="4"/>
-      <x:c r="C27" s="4"/>
-      <x:c r="D27" s="4"/>
-      <x:c r="E27" s="4"/>
-      <x:c r="F27" s="4"/>
-      <x:c r="G27" s="4"/>
-      <x:c r="H27" s="4"/>
-      <x:c r="I27" s="4"/>
-      <x:c r="J27" s="4"/>
-      <x:c r="K27" s="4"/>
-    </x:row>
-    <x:row r="28" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A28" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B28" s="9"/>
-      <x:c r="C28" s="9"/>
-      <x:c r="D28" s="9"/>
-      <x:c r="E28" s="9"/>
-      <x:c r="F28" s="9"/>
-      <x:c r="G28" s="9"/>
-      <x:c r="H28" s="9"/>
-      <x:c r="I28" s="9"/>
-      <x:c r="J28" s="9"/>
-      <x:c r="K28" s="10" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:11">
-      <x:c r="A29" s="4"/>
-      <x:c r="B29" s="4"/>
-      <x:c r="C29" s="4"/>
-      <x:c r="D29" s="4"/>
-      <x:c r="E29" s="4"/>
-      <x:c r="F29" s="4"/>
-      <x:c r="G29" s="4"/>
-      <x:c r="H29" s="4"/>
-      <x:c r="I29" s="4"/>
-      <x:c r="J29" s="4"/>
-      <x:c r="K29" s="4"/>
-    </x:row>
-    <x:row r="30" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A30" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B30" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="I30" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="J30" s="11" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K30" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A31" s="12" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="I31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="J31" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K31" s="12" t="s">
-        <x:v>86</x:v>
+      <x:c r="C24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="K24" s="12" t="s">
+        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="5">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="A17:F17"/>
-    <x:mergeCell ref="A28:J28"/>
+    <x:mergeCell ref="A21:J21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
